--- a/results/Int Task Remove ACC -0.1/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_7_permute.xlsx
@@ -440,667 +440,667 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6709620261772897</v>
+        <v>0.632647344701927</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6709972731298797</v>
+        <v>0.6407300929358473</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6590083332089323</v>
+        <v>0.6330487452914217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6553507362051721</v>
+        <v>0.6460422233611827</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6552097483948123</v>
+        <v>0.6437611235235674</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6382022644301024</v>
+        <v>0.6601517858179532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5608190313639825</v>
+        <v>0.6633414276923282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5615337151614974</v>
+        <v>0.6531674984947478</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5443618145297062</v>
+        <v>0.6496900756192268</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5446574742614312</v>
+        <v>0.6496900756192268</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5462943842067114</v>
+        <v>0.6629439664681227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5561197832436817</v>
+        <v>0.656118290431572</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5346813426683851</v>
+        <v>0.6710795851309279</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5354273340532005</v>
+        <v>0.6642930954122567</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5206343953862154</v>
+        <v>0.6692077646133865</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5169063044772753</v>
+        <v>0.6362012741980696</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5166419523328507</v>
+        <v>0.6376756334914055</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5335005697566219</v>
+        <v>0.6838302738978486</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5414952006090674</v>
+        <v>0.6651761352421424</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5505001749907529</v>
+        <v>0.6537961382609403</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.540661091842777</v>
+        <v>0.6527721106206947</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5577135675057929</v>
+        <v>0.6500230556536941</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.557241673011118</v>
+        <v>0.6236307595593882</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5520313440782632</v>
+        <v>0.6269045794499485</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5444204903390176</v>
+        <v>0.6296693918781069</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5444204903390176</v>
+        <v>0.6242691440712966</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4834689719003001</v>
+        <v>0.6301296756119286</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4758796810026389</v>
+        <v>0.6406637457309721</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4617485557042839</v>
+        <v>0.6780346382169853</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.465110492976319</v>
+        <v>0.6806858310567948</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4639454775257137</v>
+        <v>0.6786651439983148</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4639454775257137</v>
+        <v>0.650886813327163</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4616820011643934</v>
+        <v>0.6465713423200622</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4675365199895835</v>
+        <v>0.6574539425997157</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4670059496855972</v>
+        <v>0.6587499937799495</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4710962548661528</v>
+        <v>0.6228200796498194</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4738668726747378</v>
+        <v>0.6564355130048816</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4989668496190841</v>
+        <v>0.6532987415593916</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4989668496190841</v>
+        <v>0.6393301669129807</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5144607879725787</v>
+        <v>0.6382493294785607</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4918983842796932</v>
+        <v>0.6324437417169662</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4925856998551972</v>
+        <v>0.6249525202815112</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4946905649298627</v>
+        <v>0.6012207471027005</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4946905649298627</v>
+        <v>0.5854253436370542</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4986477610306375</v>
+        <v>0.5962608788682493</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.518449291660654</v>
+        <v>0.5690226559117847</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5035524781510361</v>
+        <v>0.563939630678284</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5122796236123067</v>
+        <v>0.563295440785949</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5007841410276187</v>
+        <v>0.5713605655435744</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5014283309199538</v>
+        <v>0.5904689752176603</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5020901442885838</v>
+        <v>0.5860614474637952</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4952702736324597</v>
+        <v>0.6038109834480311</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4904476611780941</v>
+        <v>0.5937311843473674</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4951782168856954</v>
+        <v>0.5768843850194646</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4945164035170653</v>
+        <v>0.5371954870631244</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5019215809211978</v>
+        <v>0.5158882895524715</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5019215809211978</v>
+        <v>0.5244958027099516</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5059140239745625</v>
+        <v>0.5244958027099516</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5086257586388208</v>
+        <v>0.5388129075169725</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5263831733536356</v>
+        <v>0.5384996243089524</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.497306096147052</v>
+        <v>0.5679190116256889</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4764668537657844</v>
+        <v>0.5450352386591893</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4652141604839365</v>
+        <v>0.5600943954857361</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4627078948197761</v>
+        <v>0.5600943954857361</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4858811074675438</v>
+        <v>0.5591016754327911</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4830360563884894</v>
+        <v>0.525977626063836</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4779588365354153</v>
+        <v>0.5304693318338864</v>
       </c>
     </row>
     <row r="69">
@@ -1110,167 +1110,167 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4779764600117103</v>
+        <v>0.5310958982499265</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.494421651415103</v>
+        <v>0.5166359396174088</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4928199884224128</v>
+        <v>0.492395780981242</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4946957483052435</v>
+        <v>0.4962785438115474</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4946957483052435</v>
+        <v>0.5045414661737069</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.494682064194238</v>
+        <v>0.498426741904397</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.494682064194238</v>
+        <v>0.5109759010365091</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.494717311146828</v>
+        <v>0.5430833868257673</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4915844790666276</v>
+        <v>0.5203347962892009</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4888217399886215</v>
+        <v>0.5190111695519408</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4875725465218307</v>
+        <v>0.5244447982962037</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4951363352126179</v>
+        <v>0.5152600644563095</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5059857618898338</v>
+        <v>0.5240319942808709</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5026766950466836</v>
+        <v>0.5231410757204062</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.501349128944134</v>
+        <v>0.5251283818414335</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5032425123032598</v>
+        <v>0.5113986571325733</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5017642136446344</v>
+        <v>0.5234995579617475</v>
       </c>
     </row>
     <row r="86">
@@ -1280,47 +1280,47 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5014509304366144</v>
+        <v>0.5214651867922619</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4979558840847984</v>
+        <v>0.5214651867922619</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4996104175063735</v>
+        <v>0.4947380446483515</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4896637274854907</v>
+        <v>0.4947556681246465</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4961898044250268</v>
+        <v>0.4956897123682801</v>
       </c>
     </row>
   </sheetData>
